--- a/duoki_editor/resources/data/blank/服装店-自由画画-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/服装店-自由画画-1-blank.xlsx
@@ -139,7 +139,7 @@
     <t>画完了把帽子放在魔镜上吧！</t>
   </si>
   <si>
-    <t>时间不多了，再不放在魔镜上，他就要没有魔力了！</t>
+    <t>时间不多了，再不放在魔镜上，它就要没有魔力了！</t>
   </si>
   <si>
     <t>不好啦，魔镜的魔力消失了，我们下次再来设计吧！</t>
@@ -151,7 +151,7 @@
     <t>哈哈，我已经帮你把你画的图案变到帽子上了！</t>
   </si>
   <si>
-    <t>你可以告诉我你画的是什么吗？比如他是什么东西？他是什么颜色之类的。</t>
+    <t>你可以告诉我你画的是什么吗？比如它是什么东西？它是什么颜色之类的。</t>
   </si>
   <si>
     <t>对了{user_name}，我们使用多奇能力，把他变成你想要的样子吧！让我们一起说，哇塞！多奇！你好神奇！</t>
@@ -166,7 +166,7 @@
     <t>这个帽子忒好看了！我好喜欢！你可真是个好设计师！给你钱！</t>
   </si>
   <si>
-    <t>Prefect！{user_name}，让我们把他放在地图外面吧！</t>
+    <t>Prefect！{user_name}，让我们把它放在地图外面吧！</t>
   </si>
 </sst>
 </file>
